--- a/measurements/37/Filled_2D_sections/coronal/week37_coronal_Batch_Allmarks.xlsx
+++ b/measurements/37/Filled_2D_sections/coronal/week37_coronal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AK32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,122 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,43 +616,79 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.296252230814991</v>
+        <v>3543.537414965986</v>
       </c>
       <c r="D2" t="n">
-        <v>23.26349182245208</v>
+        <v>454.1919832002549</v>
       </c>
       <c r="E2" t="n">
-        <v>13.92054152779463</v>
+        <v>271.7820012569427</v>
       </c>
       <c r="F2" t="n">
-        <v>1.671162847796024</v>
+        <v>1.671162847796023</v>
       </c>
       <c r="G2" t="n">
         <v>0.2158579051373999</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5710746951219512</v>
+        <v>1.670386904761905</v>
       </c>
       <c r="J2" t="n">
-        <v>1.112900152439025</v>
+        <v>21.72805059523809</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7614900914634146</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>8.050063775510203</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>21.72805059523809</v>
+      </c>
+      <c r="N2" t="n">
+        <v>17.42001488095238</v>
+      </c>
+      <c r="S2" t="n">
+        <v>8</v>
+      </c>
+      <c r="W2" t="n">
+        <v>4.434523809523809</v>
+      </c>
+      <c r="X2" t="n">
+        <v>12.2563244047619</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>7.837844122023808</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.670386904761905</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>3.270089285714286</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.712518601190476</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>9.132733491969066</v>
+      <c r="AK2" s="2" t="n">
+        <v>3481.207482993198</v>
       </c>
     </row>
     <row r="3">
@@ -553,17 +699,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9.394110648423558</v>
+        <v>3580.839002267574</v>
       </c>
       <c r="D3" t="n">
-        <v>23.77251759680306</v>
+        <v>464.130105461393</v>
       </c>
       <c r="E3" t="n">
-        <v>13.83134993983478</v>
+        <v>270.0406416824886</v>
       </c>
       <c r="F3" t="n">
         <v>1.718741677436514</v>
@@ -572,24 +718,63 @@
         <v>0.2088888120867967</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5923208841463414</v>
+        <v>2.059151785714286</v>
       </c>
       <c r="J3" t="n">
-        <v>1.269245426829268</v>
+        <v>24.78050595238095</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8609946646341463</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>8.258785485347985</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>24.78050595238095</v>
+      </c>
+      <c r="N3" t="n">
+        <v>16.22953869047619</v>
+      </c>
+      <c r="O3" t="n">
+        <v>14.66517857142857</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>6.050967261904762</v>
+      </c>
+      <c r="X3" t="n">
+        <v>11.56436011904762</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>7.789806547619047</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>2.059151785714286</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>3.095238095238095</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.547991071428572</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>23.15486854518332</v>
+      <c r="AK3" s="2" t="n">
+        <v>452.0712430250077</v>
       </c>
     </row>
     <row r="4">
@@ -600,17 +785,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.356335514574658</v>
+        <v>3566.439909297052</v>
       </c>
       <c r="D4" t="n">
-        <v>25.83414952929427</v>
+        <v>504.3810146195548</v>
       </c>
       <c r="E4" t="n">
-        <v>13.88258179804174</v>
+        <v>271.040882723672</v>
       </c>
       <c r="F4" t="n">
         <v>1.860903822150604</v>
@@ -619,24 +804,63 @@
         <v>0.1761681173238701</v>
       </c>
       <c r="H4" t="n">
+        <v>13</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.904761904761905</v>
+      </c>
+      <c r="J4" t="n">
+        <v>25.27157738095238</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9.231484661172161</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="P4" t="n">
+        <v>15.6640625</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>25.27157738095238</v>
+      </c>
+      <c r="R4" t="n">
+        <v>19.17271205357143</v>
+      </c>
+      <c r="S4" t="n">
         <v>5</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.5636432926829269</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.294397865853659</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.8983422256097562</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="W4" t="n">
+        <v>4.252232142857142</v>
+      </c>
+      <c r="X4" t="n">
+        <v>11.00446428571428</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>6.94047619047619</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.904761904761905</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.423735119047619</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.154017857142857</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>13.84071732018052</v>
+      <c r="AK4" s="2" t="n">
+        <v>270.2235286320958</v>
       </c>
     </row>
     <row r="5">
@@ -647,17 +871,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9.176383105294468</v>
+        <v>3497.845804988662</v>
       </c>
       <c r="D5" t="n">
-        <v>25.32022107810509</v>
+        <v>494.3471734296708</v>
       </c>
       <c r="E5" t="n">
-        <v>14.17281336900665</v>
+        <v>276.7073086329869</v>
       </c>
       <c r="F5" t="n">
         <v>1.786534572837584</v>
@@ -666,23 +890,62 @@
         <v>0.1798648972973242</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5423971036585366</v>
+        <v>2.256324404761905</v>
       </c>
       <c r="J5" t="n">
-        <v>1.106707317073171</v>
+        <v>21.60714285714286</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8675685975609756</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>10.55499188311688</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>15.71428571428571</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>21.60714285714286</v>
+      </c>
+      <c r="R5" t="n">
+        <v>18.525390625</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>10.58965773809524</v>
+      </c>
+      <c r="U5" t="n">
+        <v>9.37313988095238</v>
+      </c>
+      <c r="V5" t="n">
+        <v>8.63095238095238</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.256324404761905</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3.889508928571428</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>3.352399553571429</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AK5" s="2" t="n">
         <v>1.671910564662751</v>
       </c>
     </row>
@@ -694,42 +957,81 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9.403331350386676</v>
+        <v>3584.353741496599</v>
       </c>
       <c r="D6" t="n">
-        <v>23.1373558538716</v>
+        <v>451.7293285755884</v>
       </c>
       <c r="E6" t="n">
-        <v>14.03137462895091</v>
+        <v>273.9458856128511</v>
       </c>
       <c r="F6" t="n">
         <v>1.648972853032684</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2207314171935114</v>
+        <v>0.2207314171935113</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5125762195121951</v>
+        <v>1.225818452380952</v>
       </c>
       <c r="J6" t="n">
-        <v>1.086699695121951</v>
+        <v>21.21651785714286</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7956364329268293</v>
-      </c>
-      <c r="N6" t="inlineStr">
+        <v>7.653245192307689</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>21.21651785714286</v>
+      </c>
+      <c r="N6" t="n">
+        <v>15.74962797619047</v>
+      </c>
+      <c r="O6" t="n">
+        <v>15.16183035714286</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>4.190848214285714</v>
+      </c>
+      <c r="X6" t="n">
+        <v>10.00744047619048</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>6.89546130952381</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.225818452380952</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>3.502604166666667</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.577380952380953</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AK6" s="2" t="n">
         <v>0.2160205539210667</v>
       </c>
     </row>
@@ -741,43 +1043,82 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9.500297441998811</v>
+        <v>3621.315192743764</v>
       </c>
       <c r="D7" t="n">
-        <v>24.41748468468829</v>
+        <v>476.7223200343903</v>
       </c>
       <c r="E7" t="n">
-        <v>13.89095121767463</v>
+        <v>271.2042856784094</v>
       </c>
       <c r="F7" t="n">
-        <v>1.757797885980614</v>
+        <v>1.757797885980613</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2002374097929024</v>
+        <v>0.2002374097929025</v>
       </c>
       <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.277901785714286</v>
+      </c>
+      <c r="J7" t="n">
+        <v>21.24255952380952</v>
+      </c>
+      <c r="K7" t="n">
+        <v>8.615451388888889</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>15.8500744047619</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>21.24255952380952</v>
+      </c>
+      <c r="R7" t="n">
+        <v>17.77250744047619</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>10.96168154761905</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5.745907738095238</v>
+      </c>
+      <c r="V7" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="Z7" t="n">
         <v>5</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.5614519817073171</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.088033536585366</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.8405297256097561</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="AD7" t="n">
+        <v>1.277901785714286</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>3.785342261904762</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.260416666666667</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>4.05</v>
+      <c r="AK7" s="2" t="n">
+        <v>12.55</v>
       </c>
     </row>
     <row r="8">
@@ -788,17 +1129,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9.55116002379536</v>
+        <v>3640.702947845805</v>
       </c>
       <c r="D8" t="n">
-        <v>23.4847373206441</v>
+        <v>458.5115381649562</v>
       </c>
       <c r="E8" t="n">
-        <v>14.01218441346797</v>
+        <v>273.5712195010412</v>
       </c>
       <c r="F8" t="n">
         <v>1.676022569191388</v>
@@ -807,24 +1148,60 @@
         <v>0.2176178782459205</v>
       </c>
       <c r="H8" t="n">
+        <v>11</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.688988095238095</v>
+      </c>
+      <c r="J8" t="n">
+        <v>21.24255952380952</v>
+      </c>
+      <c r="K8" t="n">
+        <v>8.600852272727273</v>
+      </c>
+      <c r="L8" t="n">
         <v>4</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.8044016768292683</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.088033536585366</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.9139195884146341</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="n">
+        <v>15.70498511904762</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>21.24255952380952</v>
+      </c>
+      <c r="R8" t="n">
+        <v>17.84319196428571</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5.550595238095238</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4.220610119047619</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.688988095238095</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>3.835565476190476</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.693080357142857</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.6060165777439025</v>
+      <c r="AK8" s="2" t="n">
+        <v>1.796595982142857</v>
       </c>
     </row>
     <row r="9">
@@ -835,17 +1212,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9.649613325401548</v>
+        <v>3678.231292517007</v>
       </c>
       <c r="D9" t="n">
-        <v>22.34503194180931</v>
+        <v>436.2601474353245</v>
       </c>
       <c r="E9" t="n">
-        <v>14.19648561826566</v>
+        <v>277.1694811185201</v>
       </c>
       <c r="F9" t="n">
         <v>1.573983346488194</v>
@@ -854,24 +1231,60 @@
         <v>0.2428610203132067</v>
       </c>
       <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.934523809523809</v>
+      </c>
+      <c r="J9" t="n">
+        <v>22.28794642857143</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.903490823412699</v>
+      </c>
+      <c r="L9" t="n">
         <v>4</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.66015625</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.141577743902439</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.8780725990853658</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="n">
+        <v>12.88876488095238</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>22.28794642857143</v>
+      </c>
+      <c r="R9" t="n">
+        <v>17.14332217261904</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4.866071428571428</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4.239211309523809</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.934523809523809</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>3.459821428571428</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.860553075396826</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>1.229096798780488</v>
+      <c r="AK9" s="2" t="n">
+        <v>23.99665178571428</v>
       </c>
     </row>
     <row r="10">
@@ -882,43 +1295,79 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9.685306365258775</v>
+        <v>3691.836734693877</v>
       </c>
       <c r="D10" t="n">
-        <v>22.39034571298739</v>
+        <v>437.1448448726109</v>
       </c>
       <c r="E10" t="n">
-        <v>14.18464949945124</v>
+        <v>276.9383949892861</v>
       </c>
       <c r="F10" t="n">
-        <v>1.57849129186122</v>
+        <v>1.578491291861219</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2427736950378229</v>
+        <v>0.242773695037823</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5963224085365854</v>
+        <v>1.277901785714286</v>
       </c>
       <c r="J10" t="n">
-        <v>1.311451981707317</v>
+        <v>25.60453869047619</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8694740853658537</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>7.485834478021979</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>25.60453869047619</v>
+      </c>
+      <c r="N10" t="n">
+        <v>13.67931547619048</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6</v>
+      </c>
+      <c r="W10" t="n">
+        <v>4.075520833333333</v>
+      </c>
+      <c r="X10" t="n">
+        <v>11.64248511904762</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>7.322978670634921</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.277901785714286</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>3.761160714285714</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.818824404761904</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.8677020611026423</v>
+      <c r="AK10" s="2" t="n">
+        <v>8.257704658932337</v>
       </c>
     </row>
     <row r="11">
@@ -929,35 +1378,82 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9.60261748958953</v>
+        <v>3660.31746031746</v>
       </c>
       <c r="D11" t="n">
-        <v>23.6251607464581</v>
+        <v>461.2531383832296</v>
       </c>
       <c r="E11" t="n">
-        <v>14.22506057343832</v>
+        <v>277.7273731004624</v>
       </c>
       <c r="F11" t="n">
         <v>1.660812663994702</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2161971423614292</v>
+        <v>0.2161971423614291</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6027057926829269</v>
+        <v>1.380208333333333</v>
       </c>
       <c r="J11" t="n">
-        <v>1.31030868902439</v>
+        <v>25.58221726190476</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8366044207317074</v>
+        <v>7.867506377551019</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>25.58221726190476</v>
+      </c>
+      <c r="N11" t="n">
+        <v>15.63058035714286</v>
+      </c>
+      <c r="O11" t="n">
+        <v>12.35491071428571</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="W11" t="n">
+        <v>4.135044642857142</v>
+      </c>
+      <c r="X11" t="n">
+        <v>11.76711309523809</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>7.339719742063491</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.380208333333333</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>3.88578869047619</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.5078125</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AK11" s="2" t="n">
+        <v>3.15</v>
       </c>
     </row>
     <row r="12">
@@ -968,35 +1464,82 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9.573170731707318</v>
+        <v>3649.092970521542</v>
       </c>
       <c r="D12" t="n">
-        <v>23.24573762823896</v>
+        <v>453.8453536941892</v>
       </c>
       <c r="E12" t="n">
-        <v>14.16444394065113</v>
+        <v>276.5439055079505</v>
       </c>
       <c r="F12" t="n">
-        <v>1.641133088290536</v>
+        <v>1.641133088290537</v>
       </c>
       <c r="G12" t="n">
         <v>0.2226276002844429</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5612614329268293</v>
+        <v>2.659970238095238</v>
       </c>
       <c r="J12" t="n">
-        <v>1.309355945121951</v>
+        <v>25.56361607142857</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8600657393292683</v>
+        <v>8.424479166666666</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" t="n">
+        <v>25.56361607142857</v>
+      </c>
+      <c r="N12" t="n">
+        <v>15.67894345238095</v>
+      </c>
+      <c r="O12" t="n">
+        <v>14.96651785714286</v>
+      </c>
+      <c r="S12" t="n">
+        <v>7</v>
+      </c>
+      <c r="W12" t="n">
+        <v>4.789806547619047</v>
+      </c>
+      <c r="X12" t="n">
+        <v>10.95796130952381</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>6.299957482993197</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.818824404761905</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.730654761904762</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.659970238095238</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK12" s="2" t="n">
+        <v>24.55208333333333</v>
       </c>
     </row>
     <row r="13">
@@ -1007,17 +1550,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9.434265318262939</v>
+        <v>3596.145124716553</v>
       </c>
       <c r="D13" t="n">
-        <v>23.46351646504751</v>
+        <v>458.0972262223561</v>
       </c>
       <c r="E13" t="n">
-        <v>14.19648562989584</v>
+        <v>277.1694813455854</v>
       </c>
       <c r="F13" t="n">
         <v>1.652769359737637</v>
@@ -1026,16 +1569,63 @@
         <v>0.2153434910723607</v>
       </c>
       <c r="H13" t="n">
+        <v>14</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.333705357142857</v>
+      </c>
+      <c r="J13" t="n">
+        <v>25.38504464285714</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8.117293792517007</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>25.38504464285714</v>
+      </c>
+      <c r="N13" t="n">
+        <v>16.89174107142857</v>
+      </c>
+      <c r="O13" t="n">
+        <v>16.63132440476191</v>
+      </c>
+      <c r="S13" t="n">
+        <v>7</v>
+      </c>
+      <c r="W13" t="n">
+        <v>4.246651785714286</v>
+      </c>
+      <c r="X13" t="n">
+        <v>10.93005952380952</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>6.220238095238096</v>
+      </c>
+      <c r="Z13" t="n">
         <v>4</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.5598323170731707</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.300209603658537</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.8942692454268293</v>
+      <c r="AD13" t="n">
+        <v>1.333705357142857</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>3.482142857142857</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.798084077380953</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK13" s="2" t="n">
+        <v>15.99330357142857</v>
       </c>
     </row>
     <row r="14">
@@ -1046,35 +1636,82 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9.309934562760262</v>
+        <v>3548.75283446712</v>
       </c>
       <c r="D14" t="n">
-        <v>23.82374940558178</v>
+        <v>465.1303455375489</v>
       </c>
       <c r="E14" t="n">
-        <v>14.25710227722075</v>
+        <v>278.3529492219289</v>
       </c>
       <c r="F14" t="n">
-        <v>1.671009223497409</v>
+        <v>1.671009223497408</v>
       </c>
       <c r="G14" t="n">
         <v>0.2061276575865989</v>
       </c>
       <c r="H14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.925967261904762</v>
+      </c>
+      <c r="J14" t="n">
+        <v>25.35900297619047</v>
+      </c>
+      <c r="K14" t="n">
+        <v>9.406960227272727</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" t="n">
+        <v>25.35900297619047</v>
+      </c>
+      <c r="N14" t="n">
+        <v>17.12053571428571</v>
+      </c>
+      <c r="O14" t="n">
+        <v>17.02380952380952</v>
+      </c>
+      <c r="S14" t="n">
         <v>4</v>
       </c>
-      <c r="I14" t="n">
-        <v>0.5745045731707318</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.298875762195122</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.9055592606707318</v>
+      <c r="W14" t="n">
+        <v>4.326636904761904</v>
+      </c>
+      <c r="X14" t="n">
+        <v>11.21651785714286</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>7.534412202380952</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.925967261904762</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>3.988095238095238</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3.458891369047619</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK14" s="2" t="n">
+        <v>15.09644001831502</v>
       </c>
     </row>
     <row r="15">
@@ -1085,17 +1722,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9.12849494348602</v>
+        <v>3479.591836734694</v>
       </c>
       <c r="D15" t="n">
-        <v>23.88926872102226</v>
+        <v>466.4095321723393</v>
       </c>
       <c r="E15" t="n">
-        <v>14.32017021644406</v>
+        <v>279.584275654384</v>
       </c>
       <c r="F15" t="n">
         <v>1.668225192853494</v>
@@ -1104,16 +1741,63 @@
         <v>0.2010033668400965</v>
       </c>
       <c r="H15" t="n">
+        <v>14</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.286086309523809</v>
+      </c>
+      <c r="J15" t="n">
+        <v>25.29203869047619</v>
+      </c>
+      <c r="K15" t="n">
+        <v>8.03345556972789</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>25.29203869047619</v>
+      </c>
+      <c r="N15" t="n">
+        <v>17.26004464285714</v>
+      </c>
+      <c r="O15" t="n">
+        <v>16.83407738095238</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="W15" t="n">
+        <v>4.069940476190476</v>
+      </c>
+      <c r="X15" t="n">
+        <v>10.85751488095238</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>6.421750992063491</v>
+      </c>
+      <c r="Z15" t="n">
         <v>5</v>
       </c>
-      <c r="I15" t="n">
-        <v>0.5253429878048781</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.295445884146341</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.8246379573170731</v>
+      <c r="AD15" t="n">
+        <v>2.286086309523809</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>3.848586309523809</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.910342261904762</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK15" s="2" t="n">
+        <v>15.16443452380952</v>
       </c>
     </row>
     <row r="16">
@@ -1124,17 +1808,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.856632956573469</v>
+        <v>3375.963718820861</v>
       </c>
       <c r="D16" t="n">
-        <v>24.25787112771011</v>
+        <v>473.6060553505307</v>
       </c>
       <c r="E16" t="n">
-        <v>14.24526609444037</v>
+        <v>278.1218618438357</v>
       </c>
       <c r="F16" t="n">
         <v>1.702872446670368</v>
@@ -1143,16 +1827,63 @@
         <v>0.1891355391232223</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5745998475609756</v>
+        <v>1.356026785714286</v>
       </c>
       <c r="J16" t="n">
-        <v>1.296970274390244</v>
+        <v>25.32180059523809</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9148961509146343</v>
+        <v>8.422762133699633</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" t="n">
+        <v>25.32180059523809</v>
+      </c>
+      <c r="N16" t="n">
+        <v>17.73995535714286</v>
+      </c>
+      <c r="O16" t="n">
+        <v>17.16889880952381</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.909970238095238</v>
+      </c>
+      <c r="X16" t="n">
+        <v>11.21837797619048</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>7.160714285714285</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.356026785714286</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>3.753720238095238</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.692336309523809</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK16" s="2" t="n">
+        <v>22.33035714285714</v>
       </c>
     </row>
     <row r="17">
@@ -1163,17 +1894,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8.982450922070196</v>
+        <v>3423.922902494331</v>
       </c>
       <c r="D17" t="n">
-        <v>24.95364945400052</v>
+        <v>487.1902988638196</v>
       </c>
       <c r="E17" t="n">
-        <v>14.12504822742648</v>
+        <v>275.774751106898</v>
       </c>
       <c r="F17" t="n">
         <v>1.766624018001456</v>
@@ -1182,16 +1913,63 @@
         <v>0.181274442136524</v>
       </c>
       <c r="H17" t="n">
+        <v>14</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.847098214285714</v>
+      </c>
+      <c r="J17" t="n">
+        <v>24.76190476190476</v>
+      </c>
+      <c r="K17" t="n">
+        <v>8.51814944727891</v>
+      </c>
+      <c r="L17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>24.76190476190476</v>
+      </c>
+      <c r="N17" t="n">
+        <v>17.43117559523809</v>
+      </c>
+      <c r="O17" t="n">
+        <v>16.796875</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6</v>
+      </c>
+      <c r="W17" t="n">
+        <v>4.68563988095238</v>
+      </c>
+      <c r="X17" t="n">
+        <v>11.19047619047619</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>7.701202876984127</v>
+      </c>
+      <c r="Z17" t="n">
         <v>5</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.518578506097561</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.268292682926829</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.8226371951219512</v>
+      <c r="AD17" t="n">
+        <v>1.847098214285714</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>3.753720238095238</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.811383928571428</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK17" s="2" t="n">
+        <v>18.09142485119047</v>
       </c>
     </row>
     <row r="18">
@@ -1202,17 +1980,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8.427126710291494</v>
+        <v>3212.244897959184</v>
       </c>
       <c r="D18" t="n">
-        <v>21.26146105731406</v>
+        <v>415.1047158808935</v>
       </c>
       <c r="E18" t="n">
-        <v>12.73797366968015</v>
+        <v>248.6937716461363</v>
       </c>
       <c r="F18" t="n">
         <v>1.669139975373173</v>
@@ -1221,16 +1999,60 @@
         <v>0.2342627177864013</v>
       </c>
       <c r="H18" t="n">
+        <v>11</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.845238095238095</v>
+      </c>
+      <c r="J18" t="n">
+        <v>24.61867559523809</v>
+      </c>
+      <c r="K18" t="n">
+        <v>7.887412067099567</v>
+      </c>
+      <c r="L18" t="n">
         <v>3</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.6897865853658537</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.260956554878049</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.9169524898373984</v>
+      <c r="M18" t="n">
+        <v>24.61867559523809</v>
+      </c>
+      <c r="N18" t="n">
+        <v>15.62127976190476</v>
+      </c>
+      <c r="O18" t="n">
+        <v>13.4672619047619</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>9.228050595238095</v>
+      </c>
+      <c r="U18" t="n">
+        <v>6.378348214285714</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.845238095238095</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>3.264508928571428</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.907986111111111</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AK18" s="2" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="19">
@@ -1241,17 +2063,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8.35871505056514</v>
+        <v>3186.167800453515</v>
       </c>
       <c r="D19" t="n">
-        <v>20.33116507530212</v>
+        <v>396.9417943273272</v>
       </c>
       <c r="E19" t="n">
-        <v>12.92717756003868</v>
+        <v>252.38775236266</v>
       </c>
       <c r="F19" t="n">
         <v>1.572745866673257</v>
@@ -1260,16 +2082,63 @@
         <v>0.2541118109609888</v>
       </c>
       <c r="H19" t="n">
+        <v>11</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.928943452380952</v>
+      </c>
+      <c r="J19" t="n">
+        <v>24.16294642857143</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7.819264069264069</v>
+      </c>
+      <c r="L19" t="n">
         <v>3</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.6975990853658537</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.237614329268293</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.8946265243902439</v>
+      <c r="M19" t="n">
+        <v>24.16294642857143</v>
+      </c>
+      <c r="N19" t="n">
+        <v>14.61681547619047</v>
+      </c>
+      <c r="O19" t="n">
+        <v>13.61979166666667</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>8.41703869047619</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5.907738095238095</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.827752976190476</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.928943452380952</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>3.3984375</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.691964285714286</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK19" s="2" t="n">
+        <v>8.040132068452381</v>
       </c>
     </row>
     <row r="20">
@@ -1280,35 +2149,82 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8.178762641284949</v>
+        <v>3117.573696145124</v>
       </c>
       <c r="D20" t="n">
-        <v>20.7475325944947</v>
+        <v>405.0708744639442</v>
       </c>
       <c r="E20" t="n">
-        <v>12.73205564661724</v>
+        <v>248.5782292910984</v>
       </c>
       <c r="F20" t="n">
         <v>1.629550888744905</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2387616423120296</v>
+        <v>0.2387616423120297</v>
       </c>
       <c r="H20" t="n">
+        <v>12</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.806175595238095</v>
+      </c>
+      <c r="J20" t="n">
+        <v>24.61867559523809</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7.339719742063491</v>
+      </c>
+      <c r="L20" t="n">
         <v>3</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.6906440548780488</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.260956554878049</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.8928163109756099</v>
+      <c r="M20" t="n">
+        <v>24.61867559523809</v>
+      </c>
+      <c r="N20" t="n">
+        <v>14.19084821428571</v>
+      </c>
+      <c r="O20" t="n">
+        <v>13.48400297619048</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>9.04203869047619</v>
+      </c>
+      <c r="U20" t="n">
+        <v>6.904761904761904</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4.94047619047619</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.806175595238095</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.482638888888889</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK20" s="2" t="n">
+        <v>5.846354166666666</v>
       </c>
     </row>
     <row r="21">
@@ -1319,17 +2235,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7.789708506841166</v>
+        <v>2969.274376417233</v>
       </c>
       <c r="D21" t="n">
-        <v>19.53292308784113</v>
+        <v>381.3570698102315</v>
       </c>
       <c r="E21" t="n">
-        <v>12.76063055526919</v>
+        <v>249.1361203647795</v>
       </c>
       <c r="F21" t="n">
         <v>1.530717702643266</v>
@@ -1338,16 +2254,60 @@
         <v>0.2565645155284841</v>
       </c>
       <c r="H21" t="n">
+        <v>12</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.266741071428571</v>
+      </c>
+      <c r="J21" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="K21" t="n">
+        <v>6.962890625</v>
+      </c>
+      <c r="L21" t="n">
         <v>3</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.7211318597560976</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1.24390243902439</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.9049479166666666</v>
+      <c r="M21" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="N21" t="n">
+        <v>14.6391369047619</v>
+      </c>
+      <c r="O21" t="n">
+        <v>14.07924107142857</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>5.665922619047619</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4.001116071428571</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.266741071428571</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>3.813244047619047</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.983365221088435</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK21" s="2" t="n">
+        <v>5.921223958333333</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2317,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK22" s="2" t="n">
+        <v>4.430648561507936</v>
       </c>
     </row>
     <row r="23">
@@ -1371,6 +2339,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK23" s="2" t="n">
+        <v>11.21775793650794</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1380,6 +2356,120 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK24" s="2" t="n">
+        <v>7.122046876476285</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AK25" s="2" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK26" s="2" t="n">
+        <v>3.818824404761905</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK27" s="2" t="n">
+        <v>2.730654761904762</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK28" s="2" t="n">
+        <v>2.659970238095238</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK29" s="2" t="n">
+        <v>1.751155231829574</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK30" s="2" t="n">
+        <v>3.554981203007518</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK31" s="2" t="n">
+        <v>2.74852565752178</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AK32" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/37/Filled_2D_sections/coronal/week37_coronal_Batch_Allmarks.xlsx
+++ b/measurements/37/Filled_2D_sections/coronal/week37_coronal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2475,4 +2681,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week37_coronal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>coronal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3481.207482993198</v>
+      </c>
+      <c r="D10" t="n">
+        <v>206.006861282047</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2969.274376417233</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3691.836734693877</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>452.0712430250077</v>
+      </c>
+      <c r="D11" t="n">
+        <v>32.12462365368751</v>
+      </c>
+      <c r="E11" t="n">
+        <v>381.3570698102315</v>
+      </c>
+      <c r="F11" t="n">
+        <v>504.3810146195548</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.671910564662751</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0795510294485256</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.530717702643266</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.860903822150604</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.2160205539210666</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.02395021537767879</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1761681173238701</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2565645155284841</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis1_s00_idx0149.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis1_s01_idx0152.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>13</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>13</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis1_s02_idx0154.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>13</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>13</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis1_s03_idx0156.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>11</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>11</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis1_s04_idx0158.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>13</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis1_s05_idx0160.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>12</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>12</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis1_s06_idx0162.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>11</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>11</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis1_s07_idx0164.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>12</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>12</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>6</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis1_s08_idx0166.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>13</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>13</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis1_s09_idx0168.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>14</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>14</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis1_s10_idx0170.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>13</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>13</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>7</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis1_s11_idx0172.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>14</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>14</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>7</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis1_s12_idx0174.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>11</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>11</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis1_s13_idx0176.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>14</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>14</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>6</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis1_s14_idx0178.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>13</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>13</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>5</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis1_s15_idx0180.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>14</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>6</v>
+      </c>
+      <c r="E32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>14</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis1_s16_idx0182.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>11</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>11</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>6</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis1_s17_idx0184.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>11</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>11</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>5</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis1_s18_idx0186.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>12</v>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>12</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>6</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis1_s19_idx0189.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>12</v>
+      </c>
+      <c r="C36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>7</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>12</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" t="n">
+        <v>7</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.145931016569864</v>
+      </c>
+      <c r="E40" t="n">
+        <v>11</v>
+      </c>
+      <c r="F40" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.5871429486123998</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.905670209498071</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.9119095061289914</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>63</v>
+      </c>
+      <c r="C48" t="n">
+        <v>18.51211144179894</v>
+      </c>
+      <c r="D48" t="n">
+        <v>4.090938229089548</v>
+      </c>
+      <c r="E48" t="n">
+        <v>12.35491071428571</v>
+      </c>
+      <c r="F48" t="n">
+        <v>25.60453869047619</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>90</v>
+      </c>
+      <c r="C49" t="n">
+        <v>7.021164021164021</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.183669494073959</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.909970238095238</v>
+      </c>
+      <c r="F49" t="n">
+        <v>12.2563244047619</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>98</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.755728407434402</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.690372423598308</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.225818452380952</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.988095238095238</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>